--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-04_Collections_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-04_Collections_v1.0.xlsx
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Demo users of TD-CL-01; demo worklist TD-CL-02.</t>
+          <t>SIT/UAT users of TD-CL-01; seed worklist TD-CL-02.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="N5" s="27" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="N7" s="27" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="N8" s="27" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles; TD-CL-03 Collections parameters as delivered</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles; TD-CL-03 Collections parameters as delivered</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles; TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles; TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -9360,7 +9360,7 @@
       <c r="I13" s="12" t="inlineStr">
         <is>
           <t>A running promise recorded by mktcoll (TD-CL-07).
-Data: TD-CL-01 Demo users and roles; TD-CL-02 Demo worklist</t>
+Data: TD-CL-01 SIT/UAT users and roles; TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-01 Demo users and roles; TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-01 SIT/UAT users and roles; TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr"/>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr"/>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -10096,7 +10096,7 @@
       <c r="I23" s="12" t="inlineStr">
         <is>
           <t>clxhandler has the account open (first browser session).
-Data: TD-CL-02 Demo worklist; TD-CL-03 Collections parameters as delivered</t>
+Data: TD-CL-02 Seed worklist; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-03 Collections parameters as delivered</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr"/>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -10248,7 +10248,7 @@
       <c r="I25" s="12" t="inlineStr">
         <is>
           <t>The test lead sets the lock time of the account 16 minutes back, or waits 15 minutes.
-Data: TD-CL-02 Demo worklist; TD-CL-03 Collections parameters as delivered</t>
+Data: TD-CL-02 Seed worklist; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr"/>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-03 Collections parameters as delivered</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-03 Collections parameters as delivered</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr"/>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-09 Invoice booked for the test</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-09 Invoice booked for the test</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-09 Invoice booked for the test</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-09 Invoice booked for the test</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-09 Invoice booked for the test</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-09 Invoice booked for the test</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -10626,7 +10626,7 @@
       <c r="I30" s="12" t="inlineStr">
         <is>
           <t>A policy booked with direct payment to the insurer (payment status NOT_APPLICABLE).
-Data: TD-CL-02 Demo worklist; TD-CL-09 Invoice booked for the test</t>
+Data: TD-CL-02 Seed worklist; TD-CL-09 Invoice booked for the test</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M30" s="12" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-09 Invoice booked for the test</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-09 Invoice booked for the test</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M32" s="12" t="inlineStr"/>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr"/>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M44" s="12" t="inlineStr"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M46" s="12" t="inlineStr"/>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr"/>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M50" s="12" t="inlineStr"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M52" s="12" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr"/>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M54" s="12" t="inlineStr"/>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M56" s="12" t="inlineStr"/>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr"/>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M58" s="12" t="inlineStr">
         <is>
-          <t>CollectionsDemoDataIT#aSecondStartChangesNothing</t>
+          <t>CollectionsSeedDataIT#aSecondStartChangesNothing</t>
         </is>
       </c>
       <c r="N58" s="27" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr"/>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M60" s="12" t="inlineStr"/>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -12894,7 +12894,7 @@
       <c r="I61" s="12" t="inlineStr">
         <is>
           <t>An account with three dispositions.
-Data: TD-CL-02 Demo worklist</t>
+Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="L62" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M62" s="12" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr"/>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -13701,7 +13701,7 @@
       <c r="I72" s="12" t="inlineStr">
         <is>
           <t>The test lead sets the end date of the case above to yesterday.
-Data: TD-CL-02 Demo worklist</t>
+Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist</t>
+          <t>Data: TD-CL-02 Seed worklist</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="L80" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M80" s="12" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="L82" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M82" s="12" t="inlineStr"/>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr"/>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L84" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M84" s="12" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="L86" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M86" s="12" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr"/>
@@ -14881,7 +14881,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J88" s="12" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="L88" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M88" s="12" t="inlineStr"/>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J90" s="12" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="L90" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M90" s="12" t="inlineStr"/>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr"/>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -15187,8 +15187,8 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>An invoice of the second demo company.
-Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>An invoice of the second seed company.
+Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="L92" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M92" s="12" t="inlineStr"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="L94" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M94" s="12" t="inlineStr">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr"/>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J96" s="12" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="L96" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M96" s="12" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -15565,7 +15565,7 @@
       <c r="I97" s="12" t="inlineStr">
         <is>
           <t>A PR 2307 item left PENDING for more than a day (Cashiering does not pull it yet).
-Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr"/>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="L98" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M98" s="12" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="L100" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M100" s="12" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr"/>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="L102" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M102" s="12" t="inlineStr"/>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="L104" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M104" s="12" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="L106" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M106" s="12" t="inlineStr"/>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-05 Disposition lists</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-05 Disposition lists</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr"/>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -16763,7 +16763,7 @@
       <c r="I113" s="12" t="inlineStr">
         <is>
           <t>A test user holding CLX_BULK_UPDATE without CLX_ESCALATE (prepared by the test lead).
-Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CL-02 Demo worklist; TD-CL-10 Upload files</t>
+          <t>Data: TD-CL-02 Seed worklist; TD-CL-10 Upload files</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>A three-year account booked with annual policy-year invoices and no live plan (book one with the TD-CL-07 values if the demo plan exists).
+          <t>A three-year account booked with annual policy-year invoices and no live plan (book one with the TD-CL-07 values if the seed plan exists).
 Data: TD-CL-07 Plans, promises and escalations</t>
         </is>
       </c>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="M162" s="12" t="inlineStr">
         <is>
-          <t>CollectionsPlansDemoDataIT#theBrokenPromiseEscalatedTheAccountToTheTeamLead</t>
+          <t>CollectionsPlansSeedDataIT#theBrokenPromiseEscalatedTheAccountToTheTeamLead</t>
         </is>
       </c>
       <c r="N162" s="27" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="M177" s="12" t="inlineStr">
         <is>
-          <t>CollectionsPlansDemoDataIT#theThreeYearAccountHasAStatementPerBillingCycle; CollectionsPlansIT#aThreeYearAccountGetsAStatementOfAccountPerBillingCycle</t>
+          <t>CollectionsPlansSeedDataIT#theThreeYearAccountHasAStatementPerBillingCycle; CollectionsPlansIT#aThreeYearAccountGetsAStatementOfAccountPerBillingCycle</t>
         </is>
       </c>
       <c r="N177" s="27" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="L189" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M189" s="12" t="inlineStr">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="L190" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M190" s="12" t="inlineStr"/>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -22552,12 +22552,12 @@
       </c>
       <c r="L191" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M191" s="12" t="inlineStr">
         <is>
-          <t>CollectionsUnappliedDemoDataIT#theCollectorsDisposedOfTheDemoPaymentsAndCashieringAppliedOne</t>
+          <t>CollectionsUnappliedSeedDataIT#theCollectorsDisposedOfTheSeedPaymentsAndCashieringAppliedOne</t>
         </is>
       </c>
       <c r="N191" s="27" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="L192" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M192" s="12" t="inlineStr">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="L193" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M193" s="12" t="inlineStr"/>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="L194" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M194" s="12" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -22850,7 +22850,7 @@
       </c>
       <c r="L195" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M195" s="12" t="inlineStr"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="L196" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M196" s="12" t="inlineStr"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="L197" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M197" s="12" t="inlineStr"/>
@@ -23043,7 +23043,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -23068,12 +23068,12 @@
       </c>
       <c r="L198" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M198" s="12" t="inlineStr">
         <is>
-          <t>CollectionsUnappliedDemoDataIT#theCollectorsDisposedOfTheDemoPaymentsAndCashieringAppliedOne</t>
+          <t>CollectionsUnappliedSeedDataIT#theCollectorsDisposedOfTheSeedPaymentsAndCashieringAppliedOne</t>
         </is>
       </c>
       <c r="N198" s="27" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="L199" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M199" s="12" t="inlineStr"/>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="L200" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M200" s="12" t="inlineStr">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="L201" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M201" s="12" t="inlineStr"/>
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="L202" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M202" s="12" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="L203" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M203" s="12" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="L204" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M204" s="12" t="inlineStr">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="L205" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M205" s="12" t="inlineStr"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="L206" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M206" s="12" t="inlineStr"/>
@@ -23720,7 +23720,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="L207" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M207" s="12" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="L208" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M208" s="12" t="inlineStr">
@@ -23874,7 +23874,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="L209" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M209" s="12" t="inlineStr">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="L210" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M210" s="12" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="L211" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M211" s="12" t="inlineStr"/>
@@ -24100,7 +24100,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="L212" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M212" s="12" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L213" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M213" s="12" t="inlineStr"/>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="L214" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M214" s="12" t="inlineStr">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="L215" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M215" s="12" t="inlineStr"/>
@@ -24389,7 +24389,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="L216" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M216" s="12" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="L217" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M217" s="12" t="inlineStr"/>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="L218" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M218" s="12" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="L219" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M219" s="12" t="inlineStr">
@@ -24677,7 +24677,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="L220" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M220" s="12" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="L221" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M221" s="12" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="L222" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M222" s="12" t="inlineStr"/>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -24913,7 +24913,7 @@
       </c>
       <c r="L223" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M223" s="12" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="L224" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M224" s="12" t="inlineStr">
@@ -25037,7 +25037,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H225" s="12" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L225" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M225" s="12" t="inlineStr">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="L226" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M226" s="12" t="inlineStr">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H227" s="12" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="L227" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M227" s="12" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="L228" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M228" s="12" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H229" s="12" t="inlineStr">
@@ -25361,7 +25361,7 @@
       </c>
       <c r="L229" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M229" s="12" t="inlineStr"/>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="L230" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M230" s="12" t="inlineStr">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H231" s="12" t="inlineStr">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="L231" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M231" s="12" t="inlineStr">
@@ -25552,7 +25552,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="L232" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M232" s="12" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="H233" s="12" t="inlineStr">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="L233" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M233" s="12" t="inlineStr">
@@ -25696,7 +25696,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H234" s="12" t="inlineStr">
@@ -25769,7 +25769,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H235" s="12" t="inlineStr">
@@ -25838,7 +25838,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H237" s="12" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H238" s="12" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H239" s="12" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H241" s="12" t="inlineStr">
@@ -26263,7 +26263,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H244" s="12" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>COMMREC – Commission Receivables Unit (demo user commrec, commtl)</t>
+          <t>COMMREC – Commission Receivables Unit (SIT/UAT user commrec, commtl)</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
@@ -32110,17 +32110,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>ao (MKT_AO), mkttl (MKT_TL), mkthandler (MKT_HANDLER), clxhandler and mktcoll (MKT_COLLECTION), clxtl (CLX_TL), clxuh (MKT_SECTION_HEAD), upphandler (UNAPPLIED_HANDLER), proc (PROCESSOR), cashier and cashtl (CASHIER, CASHIER_TL), commrec and commtl (Commission), disb (DISBURSEMENT), comptrol (COMPTROLLERSHIP), badmin (BUSINESS_ADMIN), admin (SYSADMIN), auditor (AUDITOR). The demo password is issued by the test lead.</t>
+          <t>ao (MKT_AO), mkttl (MKT_TL), mkthandler (MKT_HANDLER), clxhandler and mktcoll (MKT_COLLECTION), clxtl (CLX_TL), clxuh (MKT_SECTION_HEAD), upphandler (UNAPPLIED_HANDLER), proc (PROCESSOR), cashier and cashtl (CASHIER, CASHIER_TL), commrec and commtl (Commission), disb (DISBURSEMENT), comptrol (COMPTROLLERSHIP), badmin (BUSINESS_ADMIN), admin (SYSADMIN), auditor (AUDITOR). The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V980, V990, V1900 (Collections users) and the UnappliedDemoData runner (upphandler); grants V1000</t>
+          <t>Seeds V980, V990, V1900 (Collections users) and the UnappliedSeedData runner (upphandler); grants V1000</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -32135,17 +32135,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Demo worklist</t>
+          <t>Seed worklist</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>The unpaid demo invoices listed by the refresh of clxtl and assigned by the V1900 rules (segment CBG to clxhandler, team T-CORP1 to mkthandler, all others to mktcoll); an effort, dispositions of every kind (Coordinate further, DP PR for reversal, PR 2307 for reversal, For check pick-up, one superseded) and one temporary reassignment recorded</t>
+          <t>The unpaid seed invoices listed by the refresh of clxtl and assigned by the V1900 rules (segment CBG to clxhandler, team T-CORP1 to mkthandler, all others to mktcoll); an effort, dispositions of every kind (Coordinate further, DP PR for reversal, PR 2307 for reversal, For check pick-up, one superseded) and one temporary reassignment recorded</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Demo runner CollectionsDemoData on the demo bookings (V988 and the Operations runners)</t>
+          <t>Seed runner CollectionsSeedData on the seed bookings (V988 and the Operations runners)</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V1900 (on the sales organisation of V819)</t>
+          <t>Seed V1900 (on the sales organisation of V819)</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -32245,7 +32245,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V1901</t>
+          <t>Seed V1901</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -32270,7 +32270,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Demo runner CollectionsPlansDemoData with DemoMultiYearAccount</t>
+          <t>Seed runner CollectionsPlansSeedData with SeedMultiYearAccount</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -32295,7 +32295,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Demo runners UnappliedDemoPayments, UnappliedDemoData and CollectorRequestDemoData</t>
+          <t>Seed runners UnappliedSeedPayments, UnappliedSeedData and CollectorRequestSeedData</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -32519,7 +32519,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I5" s="27" t="inlineStr">
@@ -32570,7 +32570,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I6" s="27" t="inlineStr">
@@ -32621,7 +32621,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -32636,7 +32636,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I7" s="27" t="inlineStr">
@@ -32672,7 +32672,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I8" s="27" t="inlineStr">
@@ -32723,7 +32723,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -32738,7 +32738,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I9" s="27" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -32789,7 +32789,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -32825,7 +32825,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I11" s="27" t="inlineStr">
@@ -32876,7 +32876,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -32942,7 +32942,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -32993,7 +32993,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
@@ -33029,7 +33029,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -33044,7 +33044,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -33095,7 +33095,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I17" s="27" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -33248,7 +33248,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -33590,7 +33590,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -33692,7 +33692,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -33841,7 +33841,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -33935,7 +33935,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -33982,7 +33982,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -34029,7 +34029,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -34076,7 +34076,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -34217,7 +34217,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -34311,7 +34311,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -34358,7 +34358,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -34405,7 +34405,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -34452,7 +34452,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -34550,7 +34550,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -34652,7 +34652,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -34703,7 +34703,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -34754,7 +34754,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -34852,7 +34852,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -34899,7 +34899,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -34993,7 +34993,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -35040,7 +35040,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -35181,7 +35181,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -35275,7 +35275,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -35369,7 +35369,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -35416,7 +35416,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -35478,7 +35478,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -35514,7 +35514,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -35529,7 +35529,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I66" s="27" t="inlineStr">
@@ -35565,7 +35565,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I67" s="27" t="inlineStr">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -35631,7 +35631,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I68" s="27" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -35682,7 +35682,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -35718,7 +35718,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -35733,7 +35733,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I70" s="27" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I71" s="27" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -35835,7 +35835,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I72" s="27" t="inlineStr">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -35886,7 +35886,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I73" s="27" t="inlineStr">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I74" s="27" t="inlineStr">
@@ -35973,7 +35973,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I75" s="27" t="inlineStr">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -36039,7 +36039,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I76" s="27" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -36090,7 +36090,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I77" s="27" t="inlineStr">
@@ -36126,7 +36126,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -36141,7 +36141,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I78" s="27" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -36192,7 +36192,7 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -36228,7 +36228,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -36275,7 +36275,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -36463,7 +36463,7 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -36510,7 +36510,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
@@ -36557,7 +36557,7 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
@@ -36745,7 +36745,7 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -36792,7 +36792,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -36886,7 +36886,7 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing Unit (demo user proc)</t>
+          <t>PROCESSOR – Processing Unit (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>CLX_TL – Collection Team Lead (demo user clxtl)</t>
+          <t>CLX_TL – Collection Team Lead (SIT/UAT user clxtl)</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>MKT_SECTION_HEAD – Section Head (demo user clxuh)</t>
+          <t>MKT_SECTION_HEAD – Section Head (SIT/UAT user clxuh)</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -37090,7 +37090,7 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -37141,7 +37141,7 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>MKT_HANDLER – Marketing Handler (demo user mkthandler)</t>
+          <t>MKT_HANDLER – Marketing Handler (SIT/UAT user mkthandler)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -37192,7 +37192,7 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing Team Lead (demo user mkttl)</t>
+          <t>MKT_TL – Marketing Team Lead (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -37243,7 +37243,7 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -37294,7 +37294,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (demo user upphandler)</t>
+          <t>UNAPPLIED_HANDLER – Unapplied Payment Handler (SIT/UAT user upphandler)</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -37345,7 +37345,7 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Collection Handler (demo user clxhandler, mktcoll)</t>
+          <t>MKT_COLLECTION – Collection Handler (SIT/UAT user clxhandler, mktcoll)</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
